--- a/docs/deliverables/out/Drop-1_Transactional/BRD-06_Renewal/BIBS_TestPlan_BRD-06_Renewal_v1.1.xlsx
+++ b/docs/deliverables/out/Drop-1_Transactional/BRD-06_Renewal/BIBS_TestPlan_BRD-06_Renewal_v1.1.xlsx
@@ -8131,7 +8131,7 @@
       </c>
       <c r="D173" s="12" t="inlineStr">
         <is>
-          <t>The user views the uploaded file and records a single response manually on the Insurer tab; every response is kept (append-only).</t>
+          <t>The user views the uploaded file and records a single response manually on the Insurer tab; every response is kept; none is overwritten.</t>
         </is>
       </c>
       <c r="E173" s="12" t="inlineStr">
@@ -10938,8 +10938,8 @@
       </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
-          <t>The third wrong attempt locks the account; the correct password is refused until the System Administrator unlocks rn.ao2.
-Message "Account is locked. Contact your administrator.".</t>
+          <t>The third wrong attempt locks the account; the correct password is refused with the same message as a wrong password until the System Administrator unlocks rn.ao2 in Administration &gt; Users, where the lock shows.
+Message "Invalid user name or password".</t>
         </is>
       </c>
       <c r="L12" s="12" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I20" s="12" t="inlineStr">
@@ -12656,7 +12656,7 @@
       </c>
       <c r="H36" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I36" s="12" t="inlineStr">
@@ -15516,7 +15516,7 @@
       </c>
       <c r="H76" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I76" s="12" t="inlineStr">
@@ -20098,7 +20098,7 @@
       </c>
       <c r="H140" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I140" s="12" t="inlineStr">
@@ -21317,7 +21317,7 @@
       </c>
       <c r="H157" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I157" s="12" t="inlineStr">
@@ -31036,7 +31036,7 @@
       </c>
       <c r="H293" s="12" t="inlineStr">
         <is>
-          <t>Direct request outside the screens, signed in as the persona (test lead tool)</t>
+          <t>System function check outside the screens, signed in as the persona (test lead tool)</t>
         </is>
       </c>
       <c r="I293" s="12" t="inlineStr">
